--- a/sample_reports/master_database_verifyrefs.xlsx
+++ b/sample_reports/master_database_verifyrefs.xlsx
@@ -582,7 +582,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-06 18:07 UTC</t>
+          <t>Generated: 2026-08-11 22:35 UTC</t>
         </is>
       </c>
     </row>

--- a/sample_reports/master_database_verifyrefs.xlsx
+++ b/sample_reports/master_database_verifyrefs.xlsx
@@ -582,7 +582,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-11 22:35 UTC</t>
+          <t>Generated: 2026-08-12 10:17 UTC</t>
         </is>
       </c>
     </row>

--- a/sample_reports/master_database_verifyrefs.xlsx
+++ b/sample_reports/master_database_verifyrefs.xlsx
@@ -582,7 +582,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-06 18:07 UTC</t>
+          <t>Generated: 2026-08-13 14:56 UTC</t>
         </is>
       </c>
     </row>

--- a/sample_reports/master_database_verifyrefs.xlsx
+++ b/sample_reports/master_database_verifyrefs.xlsx
@@ -582,7 +582,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-12 10:17 UTC</t>
+          <t>Generated: 2026-08-13 23:56 UTC</t>
         </is>
       </c>
     </row>
